--- a/拼席项目不同的结算标准.xlsx
+++ b/拼席项目不同的结算标准.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="22400" windowHeight="10080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="结算标准原版" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
